--- a/www/terminologies/CodeSystem-terminologie-ccam.xlsx
+++ b/www/terminologies/CodeSystem-terminologie-ccam.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>v83.00</t>
+    <t>v84.00</t>
   </si>
   <si>
     <t>Name</t>
@@ -70,7 +70,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T00:00:00+00:00</t>
+    <t>2026-07-31T00:00:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -130,7 +130,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>38223</t>
+    <t>38235</t>
   </si>
   <si>
     <t>Code</t>
